--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_933_Egypt_Mediterranean.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_933_Egypt_Mediterranean.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re082aab943134101"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R4e9ecf4473ae49fe"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Rda9362dbc7c04c67"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R5ef10ec08f8e497e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R056ef3997c874a63"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R8b361e2b1d7449e1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R096a553dda8645ea"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R47e155db68954d00"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R80fbd42f5a654a8c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R41a999b1eba64fdf"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R3f127a3c735e4b2b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R820f3802d2ff4888"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ933CommercialTable" displayName="EEZ933CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ933CommercialTable" displayName="EEZ933CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ933FunctionalTable" displayName="EEZ933FunctionalTable" ref="A1:O21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O21"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ933FunctionalTable" displayName="EEZ933FunctionalTable" ref="A1:E21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E21"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ933ValidationTable" displayName="EEZ933ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ933ValidationTable" displayName="EEZ933ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -6590,7 +6544,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12d89c20aa3d4298"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc92bb95bf52144fc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6600,20 +6554,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -6621,660 +6565,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>370.2435396338</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>370.2435396338</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$89,A2,'Species'!$U$2:$U$89))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>47696.60739505219</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>47696.60739505219</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2.0806967013</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.35</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2238.7211385683377</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2.0806967013</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$89,A3,'Species'!$U$2:$U$89))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>4658.09968814972</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.35</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>4658.09968814972</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>5931.7524407129</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.32347899553537</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>210.61000359113845</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>5931.7524407129</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>212.22323453305972</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$89,A4,'Species'!$U$2:$U$89))</x:f>
-        <x:v>1258855.6894174633</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.32347899553537</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>210.61000359113845</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1249286.4028402881</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>9569.286577175139</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0076598020721421</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0076598020721422196</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>726.8621348493998</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.1401616037398377</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>138.0898009948221</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>726.8621348493998</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>138.33469630550448</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$89,A5,'Species'!$U$2:$U$89))</x:f>
-        <x:v>100550.25268036236</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.1401616037398377</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>138.0898009948221</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>100372.24755202516</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>178.0051283372013</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0017734496604247</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0017734496604246838</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>7279.669204327901</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.79271996897762</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>62.046882985993975</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>7279.669204327901</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>64.84546734453846</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$89,A6,'Species'!$U$2:$U$89))</x:f>
-        <x:v>472053.55166828714</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.79271996897762</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>62.046882985993975</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>451680.7832976771</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>20372.76837061002</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0451043505146942</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.04510435051469411</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>3700.5447993996</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>3700.5447993996</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$89,A7,'Species'!$U$2:$U$89))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>46587.09885446906</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>46587.09885446906</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>20273.7557775877</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.352652864518725</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>225.24380984161837</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>20273.7557775877</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>288.3650652500327</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$89,A8,'Species'!$U$2:$U$89))</x:f>
-        <x:v>5846242.907667305</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.352652864518725</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>225.24380984161837</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>4566537.991142375</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>1279704.91652493</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.2802352502064251</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.2802352502064252</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>14303.3010086505</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.769286233227516</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>587.8766805007591</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>14303.3010086505</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1240.8406782205545</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$89,A9,'Species'!$U$2:$U$89))</x:f>
-        <x:v>17748117.724366628</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.769286233227516</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>587.8766805007591</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>8408577.117168615</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>9339540.607198013</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>2.1107159364844925</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>1.1107159364844925</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>747.5051074053999</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.7343037912692782</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>542.3801555023917</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>747.5051074053999</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>543.4062545496851</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$89,A10,'Species'!$U$2:$U$89))</x:f>
-        <x:v>406198.95067192847</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.7343037912692782</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>542.3801555023917</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>405431.9363933729</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>767.01427855558</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0018918447455787</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.00189184474557865</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1117.5968780695</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.044881135742784</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1108.8712811270877</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1117.5968780695</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1110.3667837514947</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$89,A11,'Species'!$U$2:$U$89))</x:f>
-        <x:v>1240942.4510327422</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.044881135742784</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1108.8712811270877</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1239271.08196856</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>1671.369064182043</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0013486710764905</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0013486710764904664</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>1359.3790579252002</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.449818374257383</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2817.2045053564666</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>1359.3790579252002</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2858.3724372276656</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$89,A12,'Species'!$U$2:$U$89))</x:f>
-        <x:v>3885611.6309179026</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.449818374257383</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2817.2045053564666</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>3829648.806474103</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>55962.82444379944</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0146130434595446</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.01461304345954467</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R1246bac7f0734754"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8a12df09f3ac41d5"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7284,20 +6799,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -7305,1146 +6810,402 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>2114.4409717251</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.680108674023477</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>478.7498754846293</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>2114.4409717251</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>483.6292185573336</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$89,A2,'Species'!$U$2:$U$89))</x:f>
-        <x:v>1022605.4348410193</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.680108674023477</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>478.7498754846293</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1012288.3519329902</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>10317.082908029086</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.010191841967092</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.01019184196709204</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathydemersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>2.0806967013</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.35</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2238.7211385683377</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>2.0806967013</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$89,A3,'Species'!$U$2:$U$89))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>4658.09968814972</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.35</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2238.7211385683377</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>4658.09968814972</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>3370.8985550805</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.374933822256824</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2371.0123835390827</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>3370.8985550805</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2394.714906906728</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$89,A4,'Species'!$U$2:$U$89))</x:f>
-        <x:v>8072341.019521624</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.374933822256824</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2371.0123835390827</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>7992442.217749867</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>79898.8017717572</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0099967944208987</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.009996794420898712</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>340.3275457064</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.888387517476615</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>773.370349463076</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>340.3275457064</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>843.1587292088602</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$89,A5,'Species'!$U$2:$U$89))</x:f>
-        <x:v>286950.1409525785</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.888387517476615</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>773.370349463076</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>263199.2329548695</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>23750.907997709</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0902392751341397</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.09023927513413971</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>3167.3913382056994</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.46240599647297</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2900.053410943986</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>3167.3913382056994</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2931.6355934069747</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$89,A6,'Species'!$U$2:$U$89))</x:f>
-        <x:v>9285637.185332777</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.46240599647297</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2900.053410943986</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>9185604.054157875</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>100033.1311749015</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.010890207174739</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.010890207174738974</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>9.3943489425</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.82</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>660.6934480075957</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>9.3943489425</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>660.6934480075957</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$89,A7,'Species'!$U$2:$U$89))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>6206.784794606836</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.82</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>660.6934480075957</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>6206.784794606836</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>22.8097965316</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.334319658008501</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>2159.333179468344</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>22.8097965316</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>2308.6529759721807</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$89,A8,'Species'!$U$2:$U$89))</x:f>
-        <x:v>52659.90464399826</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.334319658008501</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>2159.333179468344</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>49253.950467605835</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>3405.954176392428</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0691508832095105</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.06915088320951054</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>1108.202529127</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.046787476690605</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>1113.749383610505</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>1108.202529127</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>1114.1787117295369</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$89,A9,'Species'!$U$2:$U$89))</x:f>
-        <x:v>1234735.6662381354</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.046787476690605</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>1113.749383610505</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1234259.883730799</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>475.78250733646564</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0003854800059597</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.0003854800059597799</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>6.0514155556</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.35</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>223.872113856834</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>6.0514155556</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$89,A10,'Species'!$U$2:$U$89))</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1354.7431922582996</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.35</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>223.872113856834</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
-        <x:v>1354.7431922582996</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>885.2306450353</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.697116184450669</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>497.8702596985713</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>885.2306450353</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>547.2200455082004</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$89,A11,'Species'!$U$2:$U$89))</x:f>
-        <x:v>484415.9538614705</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.697116184450669</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>497.8702596985713</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>440730.0111368586</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>43685.9427246119</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.0991217789138625</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.0991217789138626</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>17195.877675224398</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.314853858459854</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>206.46852654296723</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>17195.877675224398</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>282.1908791647352</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$89,A12,'Species'!$U$2:$U$89))</x:f>
-        <x:v>4852519.839180815</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.314853858459854</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>206.46852654296723</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>3550407.5262166862</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>1302112.3129641288</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.3667500993475135</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.36675009934751335</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>1513.1254215854003</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.8130286749935025</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>650.1726176214379</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>1513.1254215854003</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>704.582478796613</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$89,A13,'Species'!$U$2:$U$89))</x:f>
-        <x:v>1066121.6602708115</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.8130286749935025</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>650.1726176214379</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>983792.7161417215</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>82328.94412909006</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.083685254808524</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.08368525480852418</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>2679.0030670261</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.3140745636651405</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>206.0983731510502</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>2679.0030670261</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>612.9781204078739</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$89,A14,'Species'!$U$2:$U$89))</x:f>
-        <x:v>1642170.2645925882</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.3140745636651405</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>206.0983731510502</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>552138.173780753</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>1090032.0908118351</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>2.9742016447583515</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>1.9742016447583515</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>3700.5447993996</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.1</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>12.589254117941675</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>3700.5447993996</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$89,A15,'Species'!$U$2:$U$89))</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>46587.09885446906</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.1</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>12.589254117941675</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
-        <x:v>46587.09885446906</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>5931.7524407129</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.32347899553537</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>210.61000359113845</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>5931.7524407129</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>212.22323453305972</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$89,A16,'Species'!$U$2:$U$89))</x:f>
-        <x:v>1258855.6894174633</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.32347899553537</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>210.61000359113845</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>1249286.4028402881</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>9569.286577175139</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.0076598020721421</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.0076598020721422196</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>383.72915720029994</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.630693488596651</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>427.26123215854494</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>383.72915720029994</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>429.4775130904467</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$89,A17,'Species'!$U$2:$U$89))</x:f>
-        <x:v>164803.04413467788</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.630693488596651</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>427.26123215854494</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>163952.59252056014</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>850.4516141177446</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.005187180032003</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.005187180032002821</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>237.64006336030002</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.3043565158676653</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>201.53780111553445</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>237.64006336030002</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>201.60510753136109</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$89,A18,'Species'!$U$2:$U$89))</x:f>
-        <x:v>47909.450527512745</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.3043565158676653</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>201.53780111553445</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>47893.45582659115</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>15.994700921597541</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.0003339642263342</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.0003339642263341759</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>12325.2390197657</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>2.9720641306518587</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>93.77004634449287</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>12325.2390197657</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>108.14849756813062</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$89,A19,'Species'!$U$2:$U$89))</x:f>
-        <x:v>1332956.0821557594</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>2.9720641306518587</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>93.77004634449287</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>1155738.2340903815</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>177217.8480653779</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1.153337358614649</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0.15333735861464892</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>92.0890235281</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.9969787981370755</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>993.0675665791254</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>92.0890235281</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>1015.0683099672872</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$89,A20,'Species'!$U$2:$U$89))</x:f>
-        <x:v>93476.64947920621</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.9969787981370755</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>993.0675665791254</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>91450.62250369809</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>2026.0269755081245</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.0221543267835733</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.022154326783573243</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>726.8621348493998</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.1401616037398377</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>138.0898009948221</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>726.8621348493998</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>138.33469630550448</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$89,A21,'Species'!$U$2:$U$89))</x:f>
-        <x:v>100550.25268036236</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.1401616037398377</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>138.0898009948221</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>100372.24755202516</x:v>
       </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>178.0051283372013</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.0017734496604247</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.0017734496604246838</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G21">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O21">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re0ab2ab33eea492c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R91346f1c6edf4600"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8619,7 +7380,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -8718,7 +7479,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>31057514.96436029</x:v>
+        <x:v>20349748.172774687</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8732,7 +7493,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>31057514.96436028</x:v>
+        <x:v>28131616.40013305</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8746,7 +7507,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>3.725290298461914e-9</x:v>
+        <x:v>-10707766.791585598</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8760,7 +7521,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-3.725290298461914e-9</x:v>
+        <x:v>-2925898.5642272346</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -8771,9 +7532,9 @@
         <x:v>EEZ_933</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -8785,47 +7546,19 @@
         <x:v>EEZ_933</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_933</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_933</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc58a37224ccc49ac"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4b040cb07dbc4885"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8872,7 +7605,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
